--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-12 ~ 2026-08-20  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-12 ~ 2026-08-20  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 272억(5.7%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 17종목  /  매도 16종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 275억(5.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -662,19 +662,19 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1340225040</v>
+        <v>1821625080</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.32%→0.59%</t>
+          <t>0.32%→0.71%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>123→244</t>
+          <t>123→287</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-240</v>
+        <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2463422400</v>
+        <v>-2854109700</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.70%</t>
+          <t>1.19%→0.59%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>548→308</t>
+          <t>548→263</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>459945030</v>
+        <v>455827875</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -723,869 +723,979 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-62</v>
+        <v>-79</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-960384960</v>
+        <v>-3009947400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.87%→0.69%</t>
+          <t>1.56%→1.01%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>263→201</t>
+          <t>198→119</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>아모텍</t>
+          <t>HPSP  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>859980510</v>
+        <v>4757370000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>1.01%→1.09%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>318→385</t>
+          <t>0→100</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>씨어스  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-36</v>
+        <v>-66</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-946269000</v>
+        <v>-886307400</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.00%</t>
+          <t>0.70%→0.56%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>36→0</t>
+          <t>253→187</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>아모텍</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1321133100</v>
+        <v>822317130</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.30%→0.57%</t>
+          <t>1.01%→1.06%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>47→96</t>
+          <t>318→385</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-33</v>
+        <v>-62</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1346637600</v>
+        <v>-926177700</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>1.56%→1.48%</t>
+          <t>0.87%→0.67%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>198→165</t>
+          <t>263→201</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>큐리언트</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2705559000</v>
+        <v>1419403500</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>1.39%→1.86%</t>
+          <t>1.20%→1.52%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>98→144</t>
+          <t>204→258</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-27</v>
+        <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2242938600</v>
+        <v>-946269000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>2.64%→1.92%</t>
+          <t>0.20%→0.00%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>132→105</t>
+          <t>36→0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>462141540</v>
+        <v>1257371850</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>1.92%→1.92%</t>
+          <t>0.30%→0.55%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>749→791</t>
+          <t>47→96</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-25</v>
+        <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2906992500</v>
+        <v>-2240127900</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>4.12%→3.66%</t>
+          <t>2.64%→1.95%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>168→143</t>
+          <t>132→105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>927687150</v>
+        <v>2652884400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.42%</t>
+          <t>1.39%→1.86%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>233→272</t>
+          <t>98→144</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-925657200</v>
+        <v>-890055000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.84%→0.63%</t>
+          <t>0.60%→0.39%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>98→74</t>
+          <t>74→49</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>한국피아이엠  (신규)</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1841529000</v>
+        <v>447713280</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.41%</t>
+          <t>1.92%→1.88%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→29</t>
+          <t>749→791</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-21</v>
+        <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2424384900</v>
+        <v>-2920005000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>5.25%→4.68%</t>
+          <t>4.12%→3.73%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>205→184</t>
+          <t>168→143</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>961884000</v>
+        <v>913477500</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>0.72%→1.04%</t>
+          <t>1.20%→1.42%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>94→118</t>
+          <t>233→272</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-19</v>
+        <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1718795100</v>
+        <v>-955638000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.62%</t>
+          <t>0.84%→0.66%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>50→31</t>
+          <t>98→74</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>큐리언트</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>461891700</v>
+        <v>1769075400</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.25%</t>
+          <t>0.00%→0.40%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>204→222</t>
+          <t>0→29</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-902547000</v>
+        <v>-2178604800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.53%</t>
+          <t>1.06%→0.53%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>55→40</t>
+          <t>50→26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>953868300</v>
+        <v>948142800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>1.30%→1.64%</t>
+          <t>0.72%→1.04%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>116→133</t>
+          <t>94→118</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-13</v>
+        <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-226677750</v>
+        <v>-2420012700</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>5.25%→4.74%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>205→184</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1686420000</v>
+        <v>971565300</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.90%→1.24%</t>
+          <t>1.30%→1.70%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>116→133</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-427226400</v>
+        <v>-907231500</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.49%</t>
+          <t>0.75%→0.54%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>74→62</t>
+          <t>55→40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>901193700</v>
+        <v>1584922500</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.68%→0.94%</t>
+          <t>0.90%→1.18%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>41→52</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-853203600</v>
+        <v>-918890700</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.67%→0.56%</t>
+          <t>6.40%→6.08%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>48→36</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>457675650</v>
+        <v>873711300</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.40%→1.47%</t>
+          <t>0.68%→0.92%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>122→131</t>
+          <t>41→52</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-875272800</v>
+        <v>-226677750</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>2.02%→1.66%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2240232000</v>
+        <v>3159435000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2.53%→3.33%</t>
+          <t>5.89%→6.35%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>46→54</t>
+          <t>80→90</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-346653000</v>
+        <v>-798238800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.31%→0.23%</t>
+          <t>0.67%→0.53%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>20→15</t>
+          <t>48→36</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2171526000</v>
+        <v>446901300</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>5.89%→5.94%</t>
+          <t>1.40%→1.45%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>80→87</t>
+          <t>122→131</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1227339000</v>
+        <v>-321460800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>3.00%→2.61%</t>
+          <t>0.60%→0.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>32→29</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>2131968000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>2.53%→3.21%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>46→54</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-869443200</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2.02%→1.68%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>77→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
           <t>제주반도체</t>
         </is>
       </c>
-      <c r="B22" s="11" t="n">
+      <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C22" s="11" t="n">
-        <v>394539000</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>3.37%→2.97%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="C23" s="11" t="n">
+        <v>383088000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>3.37%→2.93%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>166→171</t>
         </is>
       </c>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="17" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="17" t="n"/>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-940751700</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→2.07%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>76→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-899424000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>6.60%→6.53%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>201→195</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-335202000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0.31%→0.22%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>20→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-1221093000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>3.00%→2.64%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>32→29</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 11억(0.3%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G30" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J26" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B31" s="11" t="n">
         <v>424</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>4042712800</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→1.05%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C31" s="11" t="n">
+        <v>3168552000</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.83%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>0→424</t>
         </is>
       </c>
-      <c r="G27" s="14" t="inlineStr">
+      <c r="G31" s="14" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="H27" s="15" t="n">
+      <c r="H31" s="15" t="n">
         <v>-123</v>
       </c>
-      <c r="I27" s="15" t="n">
-        <v>-1463515500</v>
-      </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="I31" s="15" t="n">
+        <v>-1473294000</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
         <is>
           <t>1.11%→0.69%</t>
         </is>
       </c>
-      <c r="K27" s="13" t="inlineStr">
+      <c r="K31" s="13" t="inlineStr">
         <is>
           <t>345→222</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="G28" s="14" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="17" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="G32" s="14" t="inlineStr">
         <is>
           <t>녹십자</t>
         </is>
       </c>
-      <c r="H28" s="15" t="n">
+      <c r="H32" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I28" s="15" t="n">
-        <v>-322770000</v>
-      </c>
-      <c r="J28" s="16" t="inlineStr">
-        <is>
-          <t>3.09%→2.99%</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="I32" s="15" t="n">
+        <v>-320650000</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>3.09%→2.98%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
         <is>
           <t>183→178</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
-      <c r="J30" s="19" t="n"/>
-      <c r="K30" s="19" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="n"/>
-      <c r="C32" s="19" t="n"/>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="19" t="n"/>
-      <c r="F32" s="19" t="n"/>
-      <c r="G32" s="19" t="n"/>
-      <c r="H32" s="19" t="n"/>
-      <c r="I32" s="19" t="n"/>
-      <c r="J32" s="19" t="n"/>
-      <c r="K32" s="19" t="n"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 15억(4.9%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 7종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 80억(3.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 9종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1674,508 +1784,1502 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>코스맥스엔비티</t>
+          <t>PS일렉트로닉스  (신규)</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>54771680</v>
+        <v>713284000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.28%</t>
+          <t>0.00%→0.27%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>36→122</t>
+          <t>0→116</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-194</v>
+        <v>-171</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-131074160</v>
+        <v>-2115184500</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.79%→7.34%</t>
+          <t>2.38%→1.65%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>3,246→3,052</t>
+          <t>521→350</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>64563520</v>
+        <v>1048762000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>1.37%→1.60%</t>
+          <t>0.56%→0.93%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>442→516</t>
+          <t>126→221</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-43</v>
+        <v>-130</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-35032960</v>
+        <v>-1641497000</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>2.75%→2.63%</t>
+          <t>1.16%→0.58%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>950→907</t>
+          <t>250→120</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>한국피아이엠  (신규)</t>
         </is>
       </c>
       <c r="B39" s="11" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>26470040</v>
+        <v>1382667000</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>0.07%→0.17%</t>
+          <t>0.00%→0.53%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>22→51</t>
+          <t>0→33</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>씨어스  (편출)</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-30</v>
+        <v>-70</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-58710000</v>
+        <v>-1263762500</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.56%</t>
+          <t>0.47%→0.00%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>397→367</t>
+          <t>70→0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>106293600</v>
+        <v>1378877500</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.86%</t>
+          <t>3.01%→3.29%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>138→159</t>
+          <t>100→119</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-27</v>
+        <v>-34</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-46067400</v>
+        <v>-1334619000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>6.18%→6.03%</t>
+          <t>4.95%→5.09%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>1,020→993</t>
+          <t>375→341</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>39421200</v>
+        <v>2745600000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>7.48%→7.62%</t>
+          <t>0.00%→1.04%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>747→761</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-38570000</v>
+        <v>-200772000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>3.14%→3.01%</t>
+          <t>0.35%→0.25%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>321→307</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>로보티즈</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>75855600</v>
+        <v>2672670000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>1.61%→2.83%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>25→39</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-9</v>
+        <v>-24</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-158688000</v>
+        <v>-1132560000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.20%</t>
+          <t>0.42%→0.00%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>44→35</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>45622800</v>
+        <v>41269800</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.46%</t>
+          <t>0.55%→0.59%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>218→224</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-8</v>
+        <v>-23</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-21097600</v>
+        <v>-1845129000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.45%</t>
+          <t>2.02%→1.43%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>56→48</t>
+          <t>70→47</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>72608250</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→1.12%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>119→122</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-2208492000</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>5.28%→4.90%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>123→105</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>72930000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>1.33%→1.41%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>150→153</t>
+        </is>
+      </c>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="17" t="n"/>
+    </row>
+    <row r="47" ht="19" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 49억(2.2%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 6종목  /  매도 12종목</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="8" t="n"/>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>232</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>3245912000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>2.59%→4.01%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>400→632</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>일동제약  (편출)</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-216</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-1143460800</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>216→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>14584674000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>8.83%→15.58%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>299→520</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>고영  (편출)</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-2163488000</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.89%→0.00%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>194→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>221</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>4448288000</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>1.60%→3.85%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>200→421</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-184</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-6212208000</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>3.79%→1.01%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>250→66</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>134</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>3202868000</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>2.03%→3.67%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>204→338</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-4437000000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>6.38%→4.25%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>389→264</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>2273376000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>2.41%→3.50%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>201→285</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-12382800000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>16.35%→11.05%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>356→236</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>3298680000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>2.50%→4.25%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>101→156</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-102</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-2288880000</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.00%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>102→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>에임드바이오</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-101</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-896274000</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.76%→0.41%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>203→102</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-221680000</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.15%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>199→119</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="17" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-677705000</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.72%→0.38%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>150→83</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="n"/>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-2200752000</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>8.05%→6.01%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>435→373</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="n"/>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>토모큐브</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-439807000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.55%→0.29%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>101→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-191675000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>0.14%→0.06%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>42→17</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 15억(4.9%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="8" t="n"/>
+      <c r="J64" s="8" t="n"/>
+      <c r="K64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>코스맥스엔비티</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>54771680</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>0.08%→0.28%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>36→122</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-194</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-131074160</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>7.79%→7.34%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>3,246→3,052</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>74</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>64563520</v>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>1.37%→1.60%</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>442→516</t>
+        </is>
+      </c>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>새로닉스</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-35032960</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.75%→2.63%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>950→907</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>26470040</v>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>0.07%→0.17%</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>22→51</t>
+        </is>
+      </c>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-58710000</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→2.56%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>397→367</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>106293600</v>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>2.48%→2.86%</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>138→159</t>
+        </is>
+      </c>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-46067400</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>6.18%→6.03%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>1,020→993</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>39421200</v>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>7.48%→7.62%</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>747→761</t>
+        </is>
+      </c>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-38570000</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>3.14%→3.01%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>321→307</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>75855600</v>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>2.16%→2.43%</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>72→81</t>
+        </is>
+      </c>
+      <c r="G71" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I71" s="15" t="n">
+        <v>-158688000</v>
+      </c>
+      <c r="J71" s="16" t="inlineStr">
+        <is>
+          <t>2.76%→2.20%</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>44→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>45622800</v>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>3.30%→3.46%</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>183→192</t>
+        </is>
+      </c>
+      <c r="G72" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I72" s="15" t="n">
+        <v>-21097600</v>
+      </c>
+      <c r="J72" s="16" t="inlineStr">
+        <is>
+          <t>0.52%→0.45%</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>56→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
           <t>HK이노엔</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B73" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C73" s="11" t="n">
         <v>15333000</v>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>0.04%→0.10%</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>4→9</t>
         </is>
       </c>
-      <c r="G44" s="17" t="n"/>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="17" t="n"/>
-      <c r="J44" s="17" t="n"/>
-      <c r="K44" s="17" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 8억(1.5%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 1종목</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="G73" s="17" t="n"/>
+      <c r="H73" s="17" t="n"/>
+      <c r="I73" s="17" t="n"/>
+      <c r="J73" s="17" t="n"/>
+      <c r="K73" s="17" t="n"/>
+    </row>
+    <row r="75" ht="19" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="n"/>
+      <c r="C75" s="4" t="n"/>
+      <c r="D75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n"/>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="8" t="n"/>
+      <c r="J76" s="8" t="n"/>
+      <c r="K76" s="8" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B77" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C48" s="9" t="inlineStr">
+      <c r="C77" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D48" s="9" t="inlineStr">
+      <c r="D77" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E48" s="9" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G77" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H77" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I77" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K77" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
-      <c r="B49" s="11" t="n">
+      <c r="B78" s="11" t="n">
         <v>655</v>
       </c>
-      <c r="C49" s="11" t="n">
-        <v>1402230550</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.52%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="C78" s="11" t="n">
+        <v>1099024500</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.99%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>0→655</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
+      <c r="G78" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드</t>
         </is>
       </c>
-      <c r="H49" s="15" t="n">
+      <c r="H78" s="15" t="n">
         <v>-210</v>
       </c>
-      <c r="I49" s="15" t="n">
-        <v>-513544500</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>2.94%→1.77%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
+      <c r="I78" s="15" t="n">
+        <v>-476309400</v>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>2.94%→1.65%</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
         <is>
           <t>612→402</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
+    <row r="80" ht="19" customHeight="1">
+      <c r="A80" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="19" t="n"/>
-      <c r="E51" s="19" t="n"/>
-      <c r="F51" s="19" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="19" t="n"/>
-      <c r="I51" s="19" t="n"/>
-      <c r="J51" s="19" t="n"/>
-      <c r="K51" s="19" t="n"/>
+      <c r="B80" s="19" t="n"/>
+      <c r="C80" s="19" t="n"/>
+      <c r="D80" s="19" t="n"/>
+      <c r="E80" s="19" t="n"/>
+      <c r="F80" s="19" t="n"/>
+      <c r="G80" s="19" t="n"/>
+      <c r="H80" s="19" t="n"/>
+      <c r="I80" s="19" t="n"/>
+      <c r="J80" s="19" t="n"/>
+      <c r="K80" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="21">
     <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A76:E76"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G64:K64"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G29:K29"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="G35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A30:K30"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="G47:K47"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G25:K25"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G76:K76"/>
+    <mergeCell ref="A63:K63"/>
+    <mergeCell ref="A28:K28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 275억(5.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 18종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 137억(3.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-955638000</v>
+        <v>-2178604800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.84%→0.66%</t>
+          <t>1.06%→0.53%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>98→74</t>
+          <t>50→26</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2178604800</v>
+        <v>-955638000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.53%</t>
+          <t>0.84%→0.66%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>50→26</t>
+          <t>98→74</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-321460800</v>
+        <v>-869443200</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.51%</t>
+          <t>2.02%→1.68%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-869443200</v>
+        <v>-321460800</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.02%→1.68%</t>
+          <t>0.60%→0.51%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 11억(0.3%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1695,7 +1695,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 80억(3.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 9종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 9종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1981,23 +1981,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-200772000</v>
+        <v>-1132560000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.25%</t>
+          <t>0.42%→0.00%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2025,23 +2025,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1132560000</v>
+        <v>-200772000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.00%</t>
+          <t>0.35%→0.25%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2092,23 +2092,23 @@
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>72608250</v>
+        <v>72930000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>0.89%→1.12%</t>
+          <t>1.33%→1.41%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -2136,23 +2136,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>72930000</v>
+        <v>72608250</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>1.33%→1.41%</t>
+          <t>0.89%→1.12%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G45" s="17" t="n"/>
@@ -2164,7 +2164,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 49억(2.2%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 6종목  /  매도 12종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 6종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2297,23 +2297,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>14584674000</v>
+        <v>4448288000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>8.83%→15.58%</t>
+          <t>1.60%→3.85%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>299→520</t>
+          <t>200→421</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2341,23 +2341,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4448288000</v>
+        <v>14584674000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.60%→3.85%</t>
+          <t>8.83%→15.58%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>200→421</t>
+          <t>299→520</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2994,23 +2994,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>75855600</v>
+        <v>45622800</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>3.30%→3.46%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -3038,23 +3038,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>45622800</v>
+        <v>75855600</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.46%</t>
+          <t>2.16%→2.43%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-918890700</v>
+        <v>-226677750</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>6.40%→6.08%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-226677750</v>
+        <v>-918890700</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>6.40%→6.08%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -2297,23 +2297,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>4448288000</v>
+        <v>14584674000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.60%→3.85%</t>
+          <t>8.83%→15.58%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>200→421</t>
+          <t>299→520</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2341,23 +2341,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>14584674000</v>
+        <v>4448288000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>8.83%→15.58%</t>
+          <t>1.60%→3.85%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>299→520</t>
+          <t>200→421</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 137억(3.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 18종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 137억(3.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>164</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1821625080</v>
+        <v>1819875200</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-285</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-2854109700</v>
+        <v>-2851368000</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>455827875</v>
+        <v>455390000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-79</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-3009947400</v>
+        <v>-3007056000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>100</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>4757370000</v>
+        <v>4752800000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-66</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-886307400</v>
+        <v>-885456000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>67</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>822317130</v>
+        <v>821527200</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-62</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-926177700</v>
+        <v>-925288000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>54</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1419403500</v>
+        <v>1418040000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-946269000</v>
+        <v>-945360000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>49</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1257371850</v>
+        <v>1256164000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2240127900</v>
+        <v>-2237976000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2652884400</v>
+        <v>2650336000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-890055000</v>
+        <v>-2917200000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.39%</t>
+          <t>4.12%→3.73%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>74→49</t>
+          <t>168→143</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
         <v>42</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>447713280</v>
+        <v>447283200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2920005000</v>
+        <v>-889200000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>4.12%→3.73%</t>
+          <t>0.60%→0.39%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>168→143</t>
+          <t>74→49</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1017,7 @@
         <v>39</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>913477500</v>
+        <v>912600000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1031,23 +1031,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-2178604800</v>
+        <v>-954720000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.53%</t>
+          <t>0.84%→0.66%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>50→26</t>
+          <t>98→74</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
         <v>29</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1769075400</v>
+        <v>1767376000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-955638000</v>
+        <v>-2176512000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.84%→0.66%</t>
+          <t>1.06%→0.53%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>98→74</t>
+          <t>50→26</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>24</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>948142800</v>
+        <v>947232000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-21</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2420012700</v>
+        <v>-2417688000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>17</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>971565300</v>
+        <v>970632000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-15</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-907231500</v>
+        <v>-906360000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>15</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1584922500</v>
+        <v>1583400000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-226677750</v>
+        <v>-226460000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>11</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>873711300</v>
+        <v>872872000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-918890700</v>
+        <v>-918008000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3159435000</v>
+        <v>3156400000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1302,7 +1302,7 @@
         <v>-12</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-798238800</v>
+        <v>-797472000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>446901300</v>
+        <v>446472000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-869443200</v>
+        <v>-321152000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>2.02%→1.68%</t>
+          <t>0.60%→0.51%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2131968000</v>
+        <v>2129920000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-321460800</v>
+        <v>-868608000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.51%</t>
+          <t>2.02%→1.68%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>383088000</v>
+        <v>382720000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>-7</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-940751700</v>
+        <v>-939848000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-899424000</v>
+        <v>-898560000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>-5</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-335202000</v>
+        <v>-334880000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>-3</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1221093000</v>
+        <v>-1219920000</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 6억(0.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1630,7 +1630,7 @@
         <v>424</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>3168552000</v>
+        <v>3162573600</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>-123</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1473294000</v>
+        <v>-1470514200</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>-5</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-320650000</v>
+        <v>-320045000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 9종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 40억(1.5%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 9종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1791,7 +1791,7 @@
         <v>116</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>713284000</v>
+        <v>710291200</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>-171</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2115184500</v>
+        <v>-2106309600</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>95</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>1048762000</v>
+        <v>1044361600</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>-130</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1641497000</v>
+        <v>-1634609600</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>33</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>1382667000</v>
+        <v>1376865600</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>-70</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-1263762500</v>
+        <v>-1258460000</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>19</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>1378877500</v>
+        <v>1373092000</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>-34</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1334619000</v>
+        <v>-1329019200</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>2745600000</v>
+        <v>2734080000</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1981,23 +1981,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1132560000</v>
+        <v>-199929600</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.00%</t>
+          <t>0.35%→0.25%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
         <v>14</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>2672670000</v>
+        <v>2661456000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2025,23 +2025,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-200772000</v>
+        <v>-1127808000</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.25%</t>
+          <t>0.42%→0.00%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
         <v>6</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>41269800</v>
+        <v>41096640</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>-23</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-1845129000</v>
+        <v>-1837387200</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>3</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>72930000</v>
+        <v>72624000</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>-18</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2208492000</v>
+        <v>-2199225600</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>3</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>72608250</v>
+        <v>72303600</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 6종목  /  매도 12종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 25억(1.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 6종목  /  매도 12종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2297,23 +2297,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>14584674000</v>
+        <v>4448288000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>8.83%→15.58%</t>
+          <t>1.60%→3.85%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>299→520</t>
+          <t>200→421</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2341,23 +2341,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>4448288000</v>
+        <v>14584674000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>1.60%→3.85%</t>
+          <t>8.83%→15.58%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>200→421</t>
+          <t>299→520</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2685,7 +2685,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 15억(4.9%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 15억(5.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2781,11 +2781,11 @@
         <v>86</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>54771680</v>
+        <v>52157280</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.28%</t>
+          <t>0.08%→0.27%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -2802,11 +2802,11 @@
         <v>-194</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-131074160</v>
+        <v>-131369040</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>7.79%→7.34%</t>
+          <t>7.91%→7.45%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2825,11 +2825,11 @@
         <v>74</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>64563520</v>
+        <v>60233040</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.37%→1.60%</t>
+          <t>1.29%→1.51%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -2846,11 +2846,11 @@
         <v>-43</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-35032960</v>
+        <v>-35131000</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>2.75%→2.63%</t>
+          <t>2.79%→2.67%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2869,11 +2869,11 @@
         <v>29</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>26470040</v>
+        <v>24552560</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.07%→0.17%</t>
+          <t>0.07%→0.16%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -2890,11 +2890,11 @@
         <v>-30</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-58710000</v>
+        <v>-57228000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.56%</t>
+          <t>2.72%→2.52%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2913,11 +2913,11 @@
         <v>21</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>106293600</v>
+        <v>102782400</v>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.86%</t>
+          <t>2.43%→2.80%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2934,11 +2934,11 @@
         <v>-27</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-46067400</v>
+        <v>-46375200</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>6.18%→6.03%</t>
+          <t>6.30%→6.14%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2957,11 +2957,11 @@
         <v>14</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>39421200</v>
+        <v>40698000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>7.48%→7.62%</t>
+          <t>7.81%→7.97%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -2978,11 +2978,11 @@
         <v>-14</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-38570000</v>
+        <v>-36176000</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>3.14%→3.01%</t>
+          <t>2.98%→2.86%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2994,23 +2994,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>45622800</v>
+        <v>75718800</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>3.30%→3.46%</t>
+          <t>2.18%→2.46%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -3022,11 +3022,11 @@
         <v>-9</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-158688000</v>
+        <v>-158346000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.20%</t>
+          <t>2.79%→2.22%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
@@ -3038,23 +3038,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>75855600</v>
+        <v>43160400</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>2.16%→2.43%</t>
+          <t>3.16%→3.32%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -3066,11 +3066,11 @@
         <v>-8</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-21097600</v>
+        <v>-20307200</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.45%</t>
+          <t>0.51%→0.44%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -3089,11 +3089,11 @@
         <v>5</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>15333000</v>
+        <v>15675000</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.04%→0.10%</t>
+          <t>0.05%→0.10%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -3110,7 +3110,7 @@
     <row r="75" ht="19" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 4억(0.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B75" s="4" t="n"/>
@@ -3206,7 +3206,7 @@
         <v>655</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>1099024500</v>
+        <v>1089789000</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>-210</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-476309400</v>
+        <v>-472306800</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-226460000</v>
+        <v>-918008000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>6.40%→6.08%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-918008000</v>
+        <v>-226460000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>6.40%→6.08%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 15억(5.0%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 15억(5.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>
@@ -2778,19 +2778,19 @@
         </is>
       </c>
       <c r="B66" s="11" t="n">
-        <v>86</v>
+        <v>155</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>52157280</v>
+        <v>94004400</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.08%→0.27%</t>
+          <t>0.08%→0.42%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>36→122</t>
+          <t>36→191</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2818,23 +2818,23 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>한선엔지니어링</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="B67" s="11" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>60233040</v>
+        <v>66884560</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.51%</t>
+          <t>0.07%→0.31%</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>442→516</t>
+          <t>22→101</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -2862,44 +2862,44 @@
     <row r="68">
       <c r="A68" s="10" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>한선엔지니어링</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>24552560</v>
+        <v>60233040</v>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>0.07%→0.16%</t>
+          <t>1.29%→1.51%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>22→51</t>
+          <t>442→516</t>
         </is>
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>덕산하이메탈</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
-        <v>-30</v>
+        <v>-34</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-57228000</v>
+        <v>-24858080</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.72%→2.52%</t>
+          <t>0.60%→0.51%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>397→367</t>
+          <t>227→193</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>2.43%→2.80%</t>
+          <t>2.43%→2.81%</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -2927,155 +2927,155 @@
       </c>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-46375200</v>
+        <v>-57228000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>6.30%→6.14%</t>
+          <t>2.72%→2.52%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>1,020→993</t>
+          <t>397→367</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>오름테라퓨틱  (신규)</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>40698000</v>
+        <v>58770800</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>7.81%→7.97%</t>
+          <t>0.00%→0.21%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>747→761</t>
+          <t>0→11</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-14</v>
+        <v>-27</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-36176000</v>
+        <v>-46375200</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.86%</t>
+          <t>6.30%→6.15%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>321→307</t>
+          <t>1,020→993</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>75718800</v>
+        <v>43160400</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>2.18%→2.46%</t>
+          <t>3.16%→3.32%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>72→81</t>
+          <t>183→192</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>-9</v>
+        <v>-14</v>
       </c>
       <c r="I71" s="15" t="n">
-        <v>-158346000</v>
+        <v>-36176000</v>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>2.79%→2.22%</t>
+          <t>2.98%→2.86%</t>
         </is>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>44→35</t>
+          <t>321→307</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>브이엠</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>43160400</v>
+        <v>75718800</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>3.16%→3.32%</t>
+          <t>2.18%→2.46%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>183→192</t>
+          <t>72→81</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
         <is>
-          <t>클래시스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-8</v>
+        <v>-11</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-20307200</v>
+        <v>-48571600</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.51%→0.44%</t>
+          <t>0.48%→0.30%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
         <is>
-          <t>56→48</t>
+          <t>30→19</t>
         </is>
       </c>
     </row>
@@ -3101,173 +3101,246 @@
           <t>4→9</t>
         </is>
       </c>
-      <c r="G73" s="17" t="n"/>
-      <c r="H73" s="17" t="n"/>
-      <c r="I73" s="17" t="n"/>
-      <c r="J73" s="17" t="n"/>
-      <c r="K73" s="17" t="n"/>
-    </row>
-    <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="G73" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I73" s="15" t="n">
+        <v>-158346000</v>
+      </c>
+      <c r="J73" s="16" t="inlineStr">
+        <is>
+          <t>2.79%→2.22%</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>44→35</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="n"/>
+      <c r="B74" s="17" t="n"/>
+      <c r="C74" s="17" t="n"/>
+      <c r="D74" s="17" t="n"/>
+      <c r="E74" s="17" t="n"/>
+      <c r="G74" s="14" t="inlineStr">
+        <is>
+          <t>클래시스</t>
+        </is>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I74" s="15" t="n">
+        <v>-20307200</v>
+      </c>
+      <c r="J74" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.44%</t>
+        </is>
+      </c>
+      <c r="K74" s="13" t="inlineStr">
+        <is>
+          <t>56→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="17" t="n"/>
+      <c r="B75" s="17" t="n"/>
+      <c r="C75" s="17" t="n"/>
+      <c r="D75" s="17" t="n"/>
+      <c r="E75" s="17" t="n"/>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-40424400</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>1.99%→1.85%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>41→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 4억(0.8%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="n"/>
+      <c r="H77" s="4" t="n"/>
+      <c r="I77" s="4" t="n"/>
+      <c r="J77" s="4" t="n"/>
+      <c r="K77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="G76" s="7" t="inlineStr">
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n"/>
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H76" s="8" t="n"/>
-      <c r="I76" s="8" t="n"/>
-      <c r="J76" s="8" t="n"/>
-      <c r="K76" s="8" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="9" t="inlineStr">
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="8" t="n"/>
+      <c r="J78" s="8" t="n"/>
+      <c r="K78" s="8" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B77" s="9" t="inlineStr">
+      <c r="B79" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C77" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D77" s="9" t="inlineStr">
+      <c r="D79" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E77" s="9" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G77" s="9" t="inlineStr">
+      <c r="G79" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H79" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I77" s="9" t="inlineStr">
+      <c r="I79" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J77" s="9" t="inlineStr">
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K79" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n">
+      <c r="B80" s="11" t="n">
         <v>655</v>
       </c>
-      <c r="C78" s="11" t="n">
+      <c r="C80" s="11" t="n">
         <v>1089789000</v>
       </c>
-      <c r="D78" s="12" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>0.00%→1.99%</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>0→655</t>
         </is>
       </c>
-      <c r="G78" s="14" t="inlineStr">
+      <c r="G80" s="14" t="inlineStr">
         <is>
           <t>한스바이오메드</t>
         </is>
       </c>
-      <c r="H78" s="15" t="n">
+      <c r="H80" s="15" t="n">
         <v>-210</v>
       </c>
-      <c r="I78" s="15" t="n">
+      <c r="I80" s="15" t="n">
         <v>-472306800</v>
       </c>
-      <c r="J78" s="16" t="inlineStr">
+      <c r="J80" s="16" t="inlineStr">
         <is>
           <t>2.94%→1.65%</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
+      <c r="K80" s="13" t="inlineStr">
         <is>
           <t>612→402</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="19" customHeight="1">
-      <c r="A80" s="18" t="inlineStr">
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B80" s="19" t="n"/>
-      <c r="C80" s="19" t="n"/>
-      <c r="D80" s="19" t="n"/>
-      <c r="E80" s="19" t="n"/>
-      <c r="F80" s="19" t="n"/>
-      <c r="G80" s="19" t="n"/>
-      <c r="H80" s="19" t="n"/>
-      <c r="I80" s="19" t="n"/>
-      <c r="J80" s="19" t="n"/>
-      <c r="K80" s="19" t="n"/>
+      <c r="B82" s="19" t="n"/>
+      <c r="C82" s="19" t="n"/>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="19" t="n"/>
+      <c r="G82" s="19" t="n"/>
+      <c r="H82" s="19" t="n"/>
+      <c r="I82" s="19" t="n"/>
+      <c r="J82" s="19" t="n"/>
+      <c r="K82" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="21">
     <mergeCell ref="A34:K34"/>
     <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A77:K77"/>
     <mergeCell ref="A64:E64"/>
+    <mergeCell ref="A82:K82"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G48:K48"/>
-    <mergeCell ref="A80:K80"/>
-    <mergeCell ref="A75:K75"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="G78:K78"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A47:K47"/>
     <mergeCell ref="G4:K4"/>
@@ -3277,7 +3350,6 @@
     <mergeCell ref="G29:K29"/>
     <mergeCell ref="A35:E35"/>
     <mergeCell ref="G35:K35"/>
-    <mergeCell ref="G76:K76"/>
     <mergeCell ref="A63:K63"/>
     <mergeCell ref="A28:K28"/>
   </mergeCells>

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-918008000</v>
+        <v>-226460000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>6.40%→6.08%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-226460000</v>
+        <v>-918008000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>6.40%→6.08%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>솔브레인홀딩스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-321152000</v>
+        <v>-868608000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.51%</t>
+          <t>2.02%→1.68%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>65→57</t>
+          <t>77→69</t>
         </is>
       </c>
     </row>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>솔브레인홀딩스</t>
         </is>
       </c>
       <c r="H22" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-868608000</v>
+        <v>-321152000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>2.02%→1.68%</t>
+          <t>0.60%→0.51%</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>77→69</t>
+          <t>65→57</t>
         </is>
       </c>
     </row>
@@ -2297,23 +2297,23 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>4448288000</v>
+        <v>14584674000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>1.60%→3.85%</t>
+          <t>8.83%→15.58%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>200→421</t>
+          <t>299→520</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2341,23 +2341,23 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>221</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>14584674000</v>
+        <v>4448288000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>8.83%→15.58%</t>
+          <t>1.60%→3.85%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>299→520</t>
+          <t>200→421</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2685,7 +2685,7 @@
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 15억(5.1%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 7억(2.6%)      오늘 2026-08-20  vs  5일전 2026-08-12      매수 8종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B63" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260820.xlsx
+++ b/reports/pdf_rolling5_20260820.xlsx
@@ -943,23 +943,23 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2917200000</v>
+        <v>-889200000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>4.12%→3.73%</t>
+          <t>0.60%→0.39%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>168→143</t>
+          <t>74→49</t>
         </is>
       </c>
     </row>
@@ -987,23 +987,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-889200000</v>
+        <v>-2917200000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.60%→0.39%</t>
+          <t>4.12%→3.73%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>74→49</t>
+          <t>168→143</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1207,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>노바렉스  (편출)</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-226460000</v>
+        <v>-918008000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>6.40%→6.08%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>13→0</t>
+          <t>398→385</t>
         </is>
       </c>
     </row>
@@ -1251,23 +1251,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>노바렉스  (편출)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-918008000</v>
+        <v>-226460000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>6.40%→6.08%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>398→385</t>
+          <t>13→0</t>
         </is>
       </c>
     </row>
@@ -1981,23 +1981,23 @@
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>케어젠  (편출)</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-199929600</v>
+        <v>-1127808000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.25%</t>
+          <t>0.42%→0.00%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>101→77</t>
+          <t>24→0</t>
         </is>
       </c>
     </row>
@@ -2025,23 +2025,23 @@
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>케어젠  (편출)</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
         <v>-24</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1127808000</v>
+        <v>-199929600</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.00%</t>
+          <t>0.35%→0.25%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>24→0</t>
+          <t>101→77</t>
         </is>
       </c>
     </row>
